--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -433,10 +433,7 @@
 </t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-AdministrativeGender</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J143-AdministrativeGender-CISIS/FHIR/JDV-J143-AdministrativeGender-CISIS</t>
   </si>
   <si>
     <t>Patient.birthTime</t>
@@ -467,6 +464,9 @@
   </si>
   <si>
     <t>Patient.maritalStatusCode</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-MaritalStatus</t>
@@ -844,7 +844,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="104.4296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -1394,7 +1394,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1495,7 +1495,7 @@
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1598,7 +1598,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -2006,7 +2006,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2540,11 +2540,11 @@
         <v>74</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>74</v>
@@ -2582,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2608,7 +2608,7 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -2661,7 +2661,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2707,7 +2707,7 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2760,7 +2760,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2780,10 +2780,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2806,7 +2806,7 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2859,7 +2859,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2879,10 +2879,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2905,7 +2905,7 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -2958,7 +2958,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -2978,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3004,7 +3004,7 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -3057,7 +3057,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3077,10 +3077,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3132,7 +3132,7 @@
         <v>74</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
@@ -3154,7 +3154,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3229,7 +3229,7 @@
         <v>74</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
@@ -3326,7 +3326,7 @@
         <v>74</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
@@ -3423,7 +3423,7 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
@@ -3520,7 +3520,7 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
@@ -3617,7 +3617,7 @@
         <v>74</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="194">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,6 +313,10 @@
     <t>InfrastructureRoot.typeId</t>
   </si>
   <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
+  </si>
+  <si>
     <t>Patient.typeId.nullFlavor</t>
   </si>
   <si>
@@ -414,6 +418,103 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/PN
 </t>
+  </si>
+  <si>
+    <t>Patient.name.nullFlavor</t>
+  </si>
+  <si>
+    <t>Patient.name.use</t>
+  </si>
+  <si>
+    <t>Use Code</t>
+  </si>
+  <si>
+    <t>A set of codes advising a system or user which name in a set of like names to select for a given purpose. A name without specific use code might be a default name useful for any purpose, but a name with a specific use code would be preferred for that respective purpose</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAEntityNameUse</t>
+  </si>
+  <si>
+    <t>EN.use</t>
+  </si>
+  <si>
+    <t>Patient.name.item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>A series of items that constitute the name.</t>
+  </si>
+  <si>
+    <t>EN.item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EN-1:Can only have only one of the possible item elements in each choice {(delimiter | family | given | prefix | suffix | xmlText).count() = 1}
+</t>
+  </si>
+  <si>
+    <t>Patient.name.item.delimiter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ENXP
+</t>
+  </si>
+  <si>
+    <t>EN.item.delimiter</t>
+  </si>
+  <si>
+    <t>Patient.name.item.family</t>
+  </si>
+  <si>
+    <t>EN.item.family</t>
+  </si>
+  <si>
+    <t>Patient.name.item.given</t>
+  </si>
+  <si>
+    <t>EN.item.given</t>
+  </si>
+  <si>
+    <t>Patient.name.item.prefix</t>
+  </si>
+  <si>
+    <t>EN.item.prefix</t>
+  </si>
+  <si>
+    <t>Patient.name.item.suffix</t>
+  </si>
+  <si>
+    <t>EN.item.suffix</t>
+  </si>
+  <si>
+    <t>Patient.name.item.xmlText</t>
+  </si>
+  <si>
+    <t>Allows for mixed text content</t>
+  </si>
+  <si>
+    <t>This element is represented in XML as textual content. The actual name "xmlText" will not appear in a CDA instance.</t>
+  </si>
+  <si>
+    <t>EN.item.xmlText</t>
+  </si>
+  <si>
+    <t>Patient.name.validTime</t>
+  </si>
+  <si>
+    <t>Valid Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IVL-TS
+</t>
+  </si>
+  <si>
+    <t>An interval of time specifying the time during which the name is or was used for the entity. This accomodates the fact that people change names for people, places and things.</t>
+  </si>
+  <si>
+    <t>EN.validTime</t>
   </si>
   <si>
     <t>Patient.sdtcDesc</t>
@@ -816,7 +917,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK31"/>
+  <dimension ref="A1:AK41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.07421875" customWidth="true" bestFit="true"/>
@@ -1091,7 +1192,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>74</v>
@@ -1370,7 +1471,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1378,10 +1479,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1479,17 +1580,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1507,11 +1608,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1562,7 +1663,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1582,17 +1683,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1610,11 +1711,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1665,7 +1766,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1685,17 +1786,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1713,11 +1814,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1726,7 +1827,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1768,7 +1869,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1788,17 +1889,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1816,11 +1917,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1871,7 +1972,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1891,10 +1992,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1921,7 +2022,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1972,7 +2073,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1992,10 +2093,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2029,7 +2130,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2051,7 +2152,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2069,7 +2170,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2089,10 +2190,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2126,7 +2227,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2148,7 +2249,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2166,7 +2267,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2186,10 +2287,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2265,7 +2366,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2285,10 +2386,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2311,7 +2412,7 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -2364,7 +2465,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2384,21 +2485,23 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>74</v>
@@ -2410,11 +2513,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2441,13 +2544,11 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2465,7 +2566,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2485,21 +2586,23 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="F17" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -2511,10 +2614,12 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2562,13 +2667,13 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>74</v>
@@ -2582,10 +2687,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2596,7 +2701,7 @@
         <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>74</v>
@@ -2608,10 +2713,12 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+      <c r="M18" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2661,19 +2768,19 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>74</v>
@@ -2681,10 +2788,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2695,7 +2802,7 @@
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
@@ -2707,7 +2814,7 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2760,13 +2867,13 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>74</v>
@@ -2780,10 +2887,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2794,7 +2901,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>74</v>
@@ -2806,7 +2913,7 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2859,13 +2966,13 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>74</v>
@@ -2879,10 +2986,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2893,7 +3000,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
@@ -2905,7 +3012,7 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -2958,13 +3065,13 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>74</v>
@@ -2978,10 +3085,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2992,7 +3099,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -3057,13 +3164,13 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>74</v>
@@ -3077,10 +3184,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3091,7 +3198,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3103,7 +3210,7 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -3132,11 +3239,13 @@
         <v>74</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>74</v>
@@ -3154,13 +3263,13 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>74</v>
@@ -3174,10 +3283,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3188,7 +3297,7 @@
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
@@ -3200,11 +3309,15 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L24" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
+      <c r="N24" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>74</v>
@@ -3229,11 +3342,13 @@
         <v>74</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>74</v>
@@ -3251,7 +3366,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3271,21 +3386,23 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E25" s="2"/>
+      <c r="E25" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -3297,10 +3414,12 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
+      <c r="M25" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3326,11 +3445,13 @@
         <v>74</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -3348,7 +3469,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3368,10 +3489,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3382,7 +3503,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
@@ -3394,10 +3515,12 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
+      <c r="M26" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3423,11 +3546,13 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -3445,13 +3570,13 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>74</v>
@@ -3465,10 +3590,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3476,10 +3601,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>74</v>
@@ -3491,7 +3616,7 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -3520,11 +3645,11 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -3542,7 +3667,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3562,10 +3687,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3573,10 +3698,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
@@ -3588,7 +3713,7 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -3617,11 +3742,13 @@
         <v>74</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>154</v>
+        <v>74</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>74</v>
@@ -3639,13 +3766,13 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>74</v>
@@ -3659,10 +3786,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3673,7 +3800,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>74</v>
@@ -3685,7 +3812,7 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -3738,13 +3865,13 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>74</v>
@@ -3758,10 +3885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3784,7 +3911,7 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -3837,7 +3964,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -3857,10 +3984,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3871,7 +3998,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>74</v>
@@ -3883,7 +4010,7 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -3936,21 +4063,999 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y33" s="2"/>
+      <c r="Z33" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y34" s="2"/>
+      <c r="Z34" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y35" s="2"/>
+      <c r="Z35" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y36" s="2"/>
+      <c r="Z36" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AI36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y37" s="2"/>
+      <c r="Z37" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y38" s="2"/>
+      <c r="Z38" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK41" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="203">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -420,6 +420,9 @@
 </t>
   </si>
   <si>
+    <t>Noms et prénoms.</t>
+  </si>
+  <si>
     <t>Patient.name.nullFlavor</t>
   </si>
   <si>
@@ -534,6 +537,9 @@
 </t>
   </si>
   <si>
+    <t>Sexe.</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J143-AdministrativeGender-CISIS/FHIR/JDV-J143-AdministrativeGender-CISIS</t>
   </si>
   <si>
@@ -544,6 +550,9 @@
 </t>
   </si>
   <si>
+    <t>Date de naissance.</t>
+  </si>
+  <si>
     <t>Patient.sdtcDeceasedInd</t>
   </si>
   <si>
@@ -551,10 +560,19 @@
 </t>
   </si>
   <si>
+    <t>Patient décédé ou pas ?</t>
+  </si>
+  <si>
     <t>Patient.sdtcDeceasedTime</t>
   </si>
   <si>
+    <t>Date de décès.</t>
+  </si>
+  <si>
     <t>Patient.sdtcMultipleBirthInd</t>
+  </si>
+  <si>
+    <t>Patient né d'une grossesse multiple.</t>
   </si>
   <si>
     <t>Patient.sdtcMultipleBirthOrderNumber</t>
@@ -564,6 +582,9 @@
 </t>
   </si>
   <si>
+    <t>Numéro d’ordre de naissance (si issu d'une grossesse multiple).</t>
+  </si>
+  <si>
     <t>Patient.maritalStatusCode</t>
   </si>
   <si>
@@ -604,11 +625,17 @@
 </t>
   </si>
   <si>
+    <t>Représentant du patient/usager.</t>
+  </si>
+  <si>
     <t>Patient.birthplace</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Birthplace
 </t>
+  </si>
+  <si>
+    <t>Lieu de naissance.</t>
   </si>
   <si>
     <t>Patient.languageCommunication</t>
@@ -2414,7 +2441,9 @@
       <c r="K15" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L15" s="2"/>
+      <c r="L15" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2485,10 +2514,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2586,17 +2615,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>80</v>
@@ -2618,7 +2647,7 @@
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2649,7 +2678,7 @@
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>74</v>
@@ -2667,7 +2696,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2687,10 +2716,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2713,11 +2742,11 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2768,7 +2797,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2780,7 +2809,7 @@
         <v>74</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>74</v>
@@ -2788,10 +2817,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2814,7 +2843,7 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2867,7 +2896,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2887,10 +2916,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2913,7 +2942,7 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2966,7 +2995,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2986,10 +3015,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3012,7 +3041,7 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -3065,7 +3094,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3085,10 +3114,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3111,7 +3140,7 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -3164,7 +3193,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3184,10 +3213,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3210,7 +3239,7 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -3263,7 +3292,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3283,10 +3312,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3312,11 +3341,11 @@
         <v>102</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3366,7 +3395,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3386,17 +3415,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>80</v>
@@ -3414,11 +3443,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3469,7 +3498,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3489,10 +3518,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3515,11 +3544,11 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3570,7 +3599,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3590,10 +3619,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3616,9 +3645,11 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="L27" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3649,7 +3680,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -3667,7 +3698,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3687,10 +3718,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3713,9 +3744,11 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L28" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3766,7 +3799,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3786,10 +3819,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3812,9 +3845,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L29" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3865,7 +3900,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -3885,10 +3920,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3911,9 +3946,11 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L30" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3964,7 +4001,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -3984,10 +4021,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4010,9 +4047,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L31" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4063,7 +4102,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4083,10 +4122,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4109,9 +4148,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="L32" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4162,7 +4203,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4182,10 +4223,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4208,7 +4249,7 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -4237,11 +4278,11 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -4259,7 +4300,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4279,10 +4320,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4305,7 +4346,7 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -4334,11 +4375,11 @@
         <v>74</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>74</v>
@@ -4356,7 +4397,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4376,10 +4417,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4402,7 +4443,7 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
@@ -4431,11 +4472,11 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>74</v>
@@ -4453,7 +4494,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4473,10 +4514,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4499,7 +4540,7 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -4528,11 +4569,11 @@
         <v>74</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>74</v>
@@ -4550,7 +4591,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4570,10 +4611,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4596,7 +4637,7 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
@@ -4625,11 +4666,11 @@
         <v>74</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -4647,7 +4688,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4667,10 +4708,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4693,7 +4734,7 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -4722,11 +4763,11 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -4744,7 +4785,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -4764,10 +4805,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4790,9 +4831,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L39" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4843,7 +4886,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -4863,10 +4906,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4889,9 +4932,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L40" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4942,7 +4987,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -4962,10 +5007,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -4988,7 +5033,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -5041,7 +5086,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Personne physique</t>
+    <t>L'élément de l'en-tête du CDA patient permet de représenter une personne physique.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
